--- a/uploads/lab_rooms.xlsx
+++ b/uploads/lab_rooms.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC475C51-BFBA-495C-935E-0EDD1EBE3AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F49D54-511E-4DBF-ACE2-EC7E4D1D126C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C81C6726-5086-4F86-A491-46F0D6D31795}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8880" xr2:uid="{C81C6726-5086-4F86-A491-46F0D6D31795}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="84">
   <si>
     <t>class</t>
   </si>
@@ -290,10 +290,7 @@
     <t>A401,102</t>
   </si>
   <si>
-    <t>A,A507</t>
-  </si>
-  <si>
-    <t>A401B,A507</t>
+    <t>CP LAB/IT W/S</t>
   </si>
 </sst>
 </file>
@@ -819,7 +816,7 @@
         <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -827,7 +824,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
         <v>75</v>
@@ -1017,7 +1014,7 @@
         <v>49</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
